--- a/docs/Generated_paper/revised_grammar_questions/test_grammar_1_['～たら〈〉(条件) ']_revised.xlsx
+++ b/docs/Generated_paper/revised_grammar_questions/test_grammar_1_['～たら〈〉(条件) ']_revised.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 明日　あめが　やんだら、　(   )。</t>
+          <t>: もんだい1 きのうはえいがをみました。 それから、うちに（　　）、すぐねました。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1. かいものを　するでしょう　　　　2. かいものを　した　　　　3. かいものを　しています　　　　4. かいものを　しました</t>
+          <t>1. かえると 2. かえって 3. かえれば 4. かえったら</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -491,17 +491,17 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 きのう　えきで　かばんを　みつけたら、　(   )。</t>
+          <t>: もんだい1 あしたあめがふったら、テニスのれんしゅうを（　　）。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1. すぐに　けいさつに　とどけました　　　　2. すぐに　けいさつに　とどけます　　　　3. すぐに　けいさつに　とどけるでしょう　　　　4. すぐに　けいさつに　とどけたい</t>
+          <t>1. やめると 2. やめて 3. やめれば 4. やめます</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr"/>
@@ -515,17 +515,17 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 スーパーで　りんごが　やすい　(   )、　かってください。</t>
+          <t>: もんだい1 スーパーでりんごをかいました。 それからみかんも（　　）、いつもあまいものをたべすぎてしまいます。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>1. たら　　　　2. と　　　　3. ば　　　　4. なら</t>
+          <t>1. かうと 2. かって 3. かったら 4. かえば</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
@@ -539,17 +539,17 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 ともだちが　うちに　(   )、　えいがを　みましょう。</t>
+          <t>: もんだい1 でんわがきたら、すぐ（　　）。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>1. くるたら　　　　2. きたら　　　　3. くれば　　　　4. くるなら</t>
+          <t>1. きたので 2. きて 3. きまして 4. きます</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
@@ -563,12 +563,12 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 この　くすりを　のみ(   )、　きぶんが　よくなると　おもいます。</t>
+          <t>: もんだい1 きょうはひるごはんをたべたら、ちょっと（　　）。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1. たら　　　　2. たり　　　　3. ても　　　　4. て</t>
+          <t>1. ねむくなりました 2. たべました 3. たべれば 4. たべたら</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 でんわが　きたら、　(   )。</t>
+          <t>: もんだい1 えきまであるいたら、ゆうびんきょくにも（　　）。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>1. でんわを　きりました　　　　2. でんわを　きります　　　　3. でんわを　きってください　　　　4. でんわを　きるでしょう</t>
+          <t>1. あるくと 2. あるいて 3. あるけば 4. あるいたら</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -611,17 +611,17 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 せんこうを　(   )、　てつだってくれませんか。</t>
+          <t>: もんだい1 えきでともだちにであったら、いっしょに（　　）。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1. おえたたら　　　　2. おえたら　　　　3. おえば　　　　4. おえなら</t>
+          <t>1. あるくと 2. あるいて 3. あるきます 4. あるけば</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -635,17 +635,17 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 えいごの　じゅぎょうが　はじまったら、　(   )。</t>
+          <t>: もんだい1 せんしゅうテストがもうありました。 もしもっとべんきょう（　　）、いいてんがとれたかもしれません。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1. ほんを　ひらきました　　　　2. ほんを　ひらきます　　　　3. ほんを　ひらいてください　　　　4. ほんを　ひらいたでしょう</t>
+          <t>1. すると 2. して 3. すれば 4. していたら</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -659,12 +659,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 せんせいが　(   )、　あの　しけんの　こと　ききたいです。</t>
+          <t>: もんだい1 きのう、ともだちがうちにくるとしらなかったので、へやが（　　）でした。 もしやすくしておいたら、もっとよかったです。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1. みえたら　　　　2. みえるたら　　　　3. みれば　　　　4. みるなら</t>
+          <t>1. きたない 2. きたくなって 3. きたなったら 4. きたなければ</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -683,25 +683,265 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 えきに　(   )、　きっさてんで　やすみましょう。</t>
+          <t>: もんだい1 せんしゅうからびょうきでした。 もしやくを（　　）、きょうはげんきです。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>1. ついたら　　　　2. つくたら　　　　3. つけば　　　　4. つくなら</t>
+          <t>1. のむと 2. のんで 3. のめば 4. のんでいたら</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
       <c r="F11" s="1" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 あしたのてんきよほうであめが（　　）、ピクニックをちゅうしにします。</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>1. ふったら 2. ふると 3. ふれば 4. ふった</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr"/>
+      <c r="F12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 デパートでくつを（　　）、おかいけいをしてください。</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>1. 見つけたら 2. 見つけると 3. 見つけたとき 4. 見つけた</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 えきについたら、ははに（　　）。</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>1. でんわします 2. でんわした 3. でんわする 4. でんわして</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 このくすりをのんだら、（　　）。</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>1. ねつがさがりました 2. ねつがさがる 3. ねつがさがって 4. ねつがさがり</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 スーパーでたいくつを（　　）、ともだちにでんわします。</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>1. かんじたら 2. かんじたなら 3. かんじたらすぐに 4. かんじた</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 ともだちがいえにきたら、（　　）、いっしょにえいがをみましょう。</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>1. じかんがあったら 2. じかんがあれば 3. じかんがあった 4. じかんがなくて</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 あしたのしけんがおわったら、（　　）。</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>1. べんきょうします 2. べんきょうした 3. やすみます 4. べんきょうして</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 おばあさんがとうきょうに（　　）、しんかんせんでむかえにいきます。</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>1. くると 2. きたら 3. くれば 4. きた</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 この(スイッチ)をおしたら、（　　）。 だからさわらないでください。</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>1. ひがでました 2. ひがでる 3. ひがでた 4. ひがでます</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい2 たなかさんがえきについたら、（　　）。 やくそくのじかんは３じだから。</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>1. まちあわせをわすれた 2. まちあわせをわすれます 3. まちあわせをわすれて 4. まちあわせをわすれていた</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High_Q,Low_Q,Drop,Minor changes"</formula1>
     </dataValidation>
   </dataValidations>
